--- a/v2/IntegrationPlanning_v2.xlsx
+++ b/v2/IntegrationPlanning_v2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohammedamine.medrar\Documents\Guru99 Bankng project\v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohammedamine.medrar\Documents\Guru99 Banking project\v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF0CDF2-2986-4F09-96E5-0D29D99006F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14100" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
